--- a/data/trans_bre/P19C05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,12</t>
+          <t>-3,39; 1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,76</t>
+          <t>-1,29; 4,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,54</t>
+          <t>-3,85; 1,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,34</t>
+          <t>-3,11; 2,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 71,94</t>
+          <t>-74,77; 70,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,28; 193,28</t>
+          <t>-35,24; 222,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-70,26; 69,9</t>
+          <t>-67,9; 83,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,73</t>
+          <t>-1,75; 2,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,83</t>
+          <t>0,22; 4,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,36</t>
+          <t>-3,35; 1,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,27</t>
+          <t>-4,05; 2,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,16; 124,9</t>
+          <t>-39,22; 124,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 184,92</t>
+          <t>-1,5; 181,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,45; 50,87</t>
+          <t>-58,46; 48,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,85; 80,71</t>
+          <t>-63,7; 113,31</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,86</t>
+          <t>-1,54; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,75</t>
+          <t>-3,78; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,18</t>
+          <t>-0,07; 5,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,85</t>
+          <t>-1,68; 2,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 89,51</t>
+          <t>-18,81; 93,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 48,7</t>
+          <t>-39,2; 45,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 175,91</t>
+          <t>-4,52; 175,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 112,0</t>
+          <t>-33,11; 107,57</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 4,19</t>
+          <t>-5,03; 4,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 5,92</t>
+          <t>-3,51; 6,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,42</t>
+          <t>-4,22; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 4,7</t>
+          <t>-2,1; 5,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 40,61</t>
+          <t>-32,37; 39,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,27; 52,05</t>
+          <t>-21,54; 53,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 44,02</t>
+          <t>-35,16; 40,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 172,15</t>
+          <t>-26,73; 214,12</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 5,9</t>
+          <t>-8,73; 5,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 4,34</t>
+          <t>-8,43; 4,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 5,47</t>
+          <t>-6,42; 5,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,39</t>
+          <t>-4,91; 1,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 26,25</t>
+          <t>-29,88; 24,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 19,42</t>
+          <t>-29,23; 19,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 38,81</t>
+          <t>-30,55; 39,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-36,49; 16,12</t>
+          <t>-38,21; 11,92</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 11,56</t>
+          <t>-5,94; 11,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 10,52</t>
+          <t>-6,53; 10,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 10,63</t>
+          <t>-5,88; 9,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 6,02</t>
+          <t>-13,97; 5,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 33,38</t>
+          <t>-12,78; 35,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 29,47</t>
+          <t>-14,53; 30,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 54,04</t>
+          <t>-19,08; 48,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,65; 33,96</t>
+          <t>-67,44; 33,21</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 22,16</t>
+          <t>-1,08; 21,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 20,58</t>
+          <t>1,4; 20,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 5,9</t>
+          <t>-13,91; 5,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,43</t>
+          <t>-1,83; 9,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 53,03</t>
+          <t>-1,75; 51,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 54,16</t>
+          <t>2,53; 55,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 20,56</t>
+          <t>-34,36; 18,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 29,26</t>
+          <t>-4,79; 29,05</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,66</t>
+          <t>0,56; 4,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,12</t>
+          <t>1,11; 5,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,85</t>
+          <t>-0,69; 2,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,67</t>
+          <t>-0,51; 4,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 36,38</t>
+          <t>3,47; 34,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,77; 36,56</t>
+          <t>6,88; 38,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 29,42</t>
+          <t>-6,01; 27,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 45,11</t>
+          <t>-4,27; 50,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C05-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C05-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,57%</t>
+          <t>-14,06%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,11</t>
+          <t>-3,23; 1,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 4,15</t>
+          <t>-1,64; 3,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,63</t>
+          <t>-3,59; 1,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,54</t>
+          <t>-4,45; 2,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,77; 70,67</t>
+          <t>-76,62; 54,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 222,11</t>
+          <t>-41,12; 194,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,9; 83,61</t>
+          <t>-70,35; 93,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-14,63%</t>
+          <t>-9,27%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,85</t>
+          <t>-1,8; 2,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 4,94</t>
+          <t>0,21; 5,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,44</t>
+          <t>-3,22; 1,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,63</t>
+          <t>-3,88; 2,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 124,32</t>
+          <t>-38,89; 150,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 181,34</t>
+          <t>-0,79; 228,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,46; 48,71</t>
+          <t>-57,31; 55,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,7; 113,31</t>
+          <t>-60,17; 104,45</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,81</t>
+          <t>-1,18; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 2,77</t>
+          <t>-3,55; 2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,3</t>
+          <t>-0,17; 5,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,77</t>
+          <t>-1,58; 2,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 93,2</t>
+          <t>-15,3; 104,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,2; 45,97</t>
+          <t>-38,18; 47,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 175,65</t>
+          <t>-5,47; 170,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 107,57</t>
+          <t>-30,55; 112,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>-9,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 4,29</t>
+          <t>-5,38; 3,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 6,15</t>
+          <t>-2,81; 5,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,19</t>
+          <t>-4,32; 3,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,78</t>
+          <t>-3,38; 1,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 39,62</t>
+          <t>-33,87; 36,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 53,44</t>
+          <t>-17,06; 52,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 40,84</t>
+          <t>-34,3; 42,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 214,12</t>
+          <t>-36,35; 33,93</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,99</t>
+          <t>-1,7</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>-14,38%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 5,42</t>
+          <t>-9,05; 5,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 4,26</t>
+          <t>-8,19; 5,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 5,83</t>
+          <t>-6,22; 5,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 1,2</t>
+          <t>-4,62; 1,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 24,62</t>
+          <t>-30,39; 25,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,23; 19,06</t>
+          <t>-27,97; 22,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 39,66</t>
+          <t>-30,63; 40,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 11,92</t>
+          <t>-33,65; 13,83</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-17,96%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 11,49</t>
+          <t>-5,27; 11,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 10,85</t>
+          <t>-7,24; 10,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 9,81</t>
+          <t>-5,89; 10,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 5,8</t>
+          <t>0,24; 8,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 35,2</t>
+          <t>-12,09; 35,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 30,51</t>
+          <t>-15,83; 29,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 48,31</t>
+          <t>-20,44; 53,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 33,21</t>
+          <t>0,95; 57,64</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 21,94</t>
+          <t>0,12; 23,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 20,78</t>
+          <t>0,99; 20,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 5,2</t>
+          <t>-14,41; 5,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 9,37</t>
+          <t>-2,58; 8,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 51,44</t>
+          <t>0,43; 56,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 55,09</t>
+          <t>1,97; 55,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 18,47</t>
+          <t>-35,68; 17,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 29,05</t>
+          <t>-5,87; 28,0</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,36</t>
+          <t>0,46; 4,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,31</t>
+          <t>1,16; 5,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,71</t>
+          <t>-0,8; 2,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,06</t>
+          <t>0,52; 3,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 34,08</t>
+          <t>3,27; 35,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,88; 38,05</t>
+          <t>7,72; 37,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 27,68</t>
+          <t>-7,01; 28,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 50,58</t>
+          <t>4,74; 33,49</t>
         </is>
       </c>
     </row>
